--- a/build/inline-add-edit-parts/testrail-import/Inline-Add-and-Edit-Parts_testrail-import.xlsx
+++ b/build/inline-add-edit-parts/testrail-import/Inline-Add-and-Edit-Parts_testrail-import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -518,8 +518,8 @@
           <t>1. Each work order line displays an “Add Part” button in its Parts section.
 2. The “Add Part” button is shown even on a work order line that has no parts yet.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-R1, S1-E1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-R1, S1-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -567,8 +567,8 @@
           <t>1. An editable inline row opens directly below the Add Part control and above the line's existing parts.
 2. The cursor is placed in the description field automatically.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-R2, S1-R3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-R2, S1-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -617,8 +617,8 @@
           <t>1. For a Tech View user the inline row follows Story 2 (three fields).
 2. For a Full View user the inline row follows Story 4 (six fields).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-R4, S1-R5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-R4, S1-R5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -668,8 +668,8 @@
           <t>1. An Edit control is displayed on the part line when you hover over it.
 2. The Edit control is also revealed when the part line receives keyboard focus, so it can be reached without a mouse.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-R6, S1-R7, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-R6, S1-R7, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -719,8 +719,8 @@
           <t>1. For a Tech View user, selecting Edit follows Story 3 (inline edit row).
 2. For a Full View user, selecting Edit follows Story 5 (part details modal).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-R8, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-R8, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -767,8 +767,8 @@
         <is>
           <t>1. The “Add Part” button is not displayed on any work order line when the status is Complete, Invoiced, Paid, Declined, or Imported.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-N1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-N1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -815,8 +815,8 @@
         <is>
           <t>1. The Edit control is not displayed on part lines when the status is Complete, Invoiced, Paid, Declined, or Imported.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-N2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-N2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -865,8 +865,8 @@
           <t>1. The “Add Part” button is not displayed.
 2. The Edit control is not displayed on part lines.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-N3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-N3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -913,8 +913,8 @@
         <is>
           <t>1. The “Add Part” button and the Edit control are not displayed, matching today's behaviour for a non-editable work order.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-N4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-N4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -962,8 +962,8 @@
         <is>
           <t>1. The unsaved-data confirmation from S6-R5 is shown before the requested row opens.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S1-E2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9316 (Story 1, Add Part Button on Work Order Lines) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S1-E2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1012,8 +1012,8 @@
           <t>1. The inline row displays exactly three editable fields, in order: description, part number, quantity.
 2. Cost, sell price, category, and any other part details are not displayed in the inline row.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R1, S2-R2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R1, S2-R2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1061,8 +1061,8 @@
         <is>
           <t>1. The part number field is the same catalog typeahead used in the existing add-part flow and behaves as it does today.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1104,16 +1104,18 @@
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Type a description of your own into the description field.
-In the part number field, search and select a matching catalog part.</t>
+In the part number field, search and select a matching catalog part.
+Look at the typeahead result cards before selecting.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1. The part number and description populate from the selected part; the description you had typed is replaced by the catalog description.
 2. Focus moves to the quantity field, since part number and description are already populated.
----
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R4, S2-R19, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+3. The typeahead result cards also carry the part's inventory quantity and bins, and selecting the part triggers bin allocation (see the Bin Allocation cases, Story 7).
+---
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R4, S2-R19, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1162,8 +1164,8 @@
         <is>
           <t>1. The description accepts your edit; the populated catalog description can be overwritten.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1211,9 +1213,10 @@
         <is>
           <t>1. The quantity field starts empty (it is not pre-filled with 1).
 2. Quantity is a required field.
----
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R6, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+3. Quantity may also be set by applying a bin split (see the Bin Allocation cases, Story 7).
+---
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R6, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1261,8 +1264,8 @@
         <is>
           <t>1. The inline row displays a Save action and an X (close) action.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R7, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R7, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1312,8 +1315,8 @@
           <t>1. With a description and a quantity the part saves even though part number is empty (part number is optional).
 2. Without a quantity the row does not save (see the validation cases).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R8, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R8, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1362,8 +1365,8 @@
           <t>1. The part is added at the top of the line's parts list.
 2. A success toast displays reading “Part added” and fades on its own.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R9, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R9, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1412,8 +1415,8 @@
           <t>1. Immediately after the successful save, a new empty inline row opens on the same work order line.
 2. The cursor is placed in the description field of the new row.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R10, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R10, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1463,8 +1466,8 @@
           <t>1. The part is assigned the category “Uncategorized”.
 2. The category is not displayed to the Tech View user.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R11, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R11, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1513,8 +1516,8 @@
         <is>
           <t>1. Pressing Enter saves the row, with the same result as selecting Save.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R12, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R12, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1528,7 +1531,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Tab moves through fields in order and from quantity to Save</t>
+          <t>Tab moves through the Tech View add row and never leaves it</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1555,16 +1558,18 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Place the cursor in the description field and press Tab repeatedly.</t>
+          <t>Place the cursor in the description field and press Tab repeatedly through the whole row.
+For the last step, have a bin allocated so the “Pulled from” chip is shown.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. Tab moves the cursor forward in the order description, part number, quantity.
-2. Tab from the quantity field moves focus to the Save action rather than leaving the row.
----
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R13, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+          <t>1. Tab moves the cursor forward through the row and does not leave it (per the spec's Keyboard Model — Inline Row).
+2. The Tech View add-row Tab order is: description, part number, quantity, Save, Cancel (X).
+3. When a bin is allocated, the “Pulled from” bin chip (in the hint row below) is the last Tab stop; it is present only while a bin is allocated.
+---
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R13 and Keyboard Model - Inline Row, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1612,8 +1617,8 @@
         <is>
           <t>1. Escape closes the inline row, with the same result as selecting X (for an empty row it closes immediately).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R14, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R14, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1662,8 +1667,8 @@
           <t>1. Selecting X closes the inline row without saving.
 2. Because the row contains data, the discard confirmation from S6-R1 is shown first.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R15, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R15, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1712,8 +1717,8 @@
         <is>
           <t>1. The inline row remains open and its data is preserved; the click does not cancel the row.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R16, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R16, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1763,8 +1768,8 @@
 2. The success toast is the same as any other save: “Part added”.
 3. The part number typeahead behaves as in the existing add-part flow when nothing matches.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R17, S2-E1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R17, S2-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1812,8 +1817,8 @@
         <is>
           <t>1. The inline row displays a keyboard hint legend: Enter — save &amp; next row · Tab — next field · Esc — cancel.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-R18, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-R18, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1863,8 +1868,8 @@
           <t>1. The row does not save; a single inline validation message names all missing fields in order.
 2. In Tech View only description and qty can appear in the message (for example “Enter a qty to save this part.” when only quantity is missing).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-N1, S2-N2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-N1, S2-N2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1912,8 +1917,8 @@
         <is>
           <t>1. The row does not save and an inline validation message is displayed: “Qty must be greater than 0.”
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-N3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-N3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1961,8 +1966,8 @@
         <is>
           <t>1. The invalid field is highlighted and the cursor moves to the first field that failed validation.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-N4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-N4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2011,8 +2016,8 @@
         <is>
           <t>1. The validation message clears as soon as the field is corrected.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-N5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-N5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2060,8 +2065,8 @@
         <is>
           <t>1. The row closes immediately with no confirmation.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-N6, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-N6, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2109,8 +2114,8 @@
         <is>
           <t>1. Two separate part lines are created; the quantities are not merged.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-E2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-E2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2161,8 +2166,8 @@
           <t>1. The save fails and an alert is shown: “This work order can no longer be edited. Refresh to see the latest.”
 2. The entered data remains in the row so it can be copied before refreshing.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-E3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-E3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2213,8 +2218,8 @@
           <t>1. An alert toast is shown: “Couldn't add the part. Please try again.”
 2. The inline row remains open with the entered data intact.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S2-EH1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9317 (Story 2, Inline Add Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S2-EH1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2264,8 +2269,8 @@
           <t>1. An inline edit row opens directly below that part line.
 2. It contains the same three fields as the add flow in the same order: description, part number, quantity.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2315,8 +2320,8 @@
           <t>1. The inline row is pre-populated with the part's current description, part number, and quantity.
 2. The cursor is placed in the description field when the row opens.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R2, S3-R3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R2, S3-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2359,16 +2364,18 @@
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Open an edit row and exercise the fields, keyboard, and validation.
+Press Tab repeatedly through the whole edit row.
 Read the keyboard hint legend.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. All field, keyboard, and validation behaviour from Story 2 applies identically to the edit row.
-2. The edit row's hint legend reads Enter — save · Tab — next field · Esc — cancel, without “&amp; next row”, because saving an edit does not open a new row.
----
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+2. The edit-row Tab order matches the Tech View add row (per the spec's Keyboard Model — Inline Row): description, part number, quantity, Save, Cancel (X), then the “Pulled from” bin chip when one is shown; the edit row has no “More Options” button.
+3. The edit row's hint legend reads Enter — save · Tab — next field · Esc — cancel, without “&amp; next row”, because saving an edit does not open a new row.
+---
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R4 and Keyboard Model - Inline Row, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2417,8 +2424,8 @@
         <is>
           <t>1. The part line is updated in place and the inline row closes, returning to the normal part line display.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2468,8 +2475,8 @@
         <is>
           <t>1. No new empty inline row opens after an edit save; the repeat-entry behaviour applies only to the add flow.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R6, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R6, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2519,8 +2526,8 @@
         <is>
           <t>1. Cost, sell price, and category are preserved unchanged when the Tech View user saves the inline edit, because they are not displayed in Tech View and were not re-linked.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R7, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R7, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2571,8 +2578,8 @@
           <t>1. Because a field was changed, the discard confirmation from S6-R1 is shown.
 2. On Discard the row closes without saving and the part line returns to its previously saved values.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R8, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R8, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2624,8 +2631,8 @@
 2. The quantity you entered stays as it is and focus moves to it.
 3. This is the one case where the values protected by S3-R7 are overwritten.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-R9, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-R9, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2674,8 +2681,8 @@
         <is>
           <t>1. No confirmation is shown and no update is recorded.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-N1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-N1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2724,8 +2731,8 @@
         <is>
           <t>1. The Edit control is not displayed.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-N2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-N2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2774,8 +2781,8 @@
         <is>
           <t>1. The row does not save and the combined validation from S2-N1 applies (the description is named as missing).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-N3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-N3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2826,8 +2833,8 @@
         <is>
           <t>1. The save fails and an alert is shown: “This part was changed by someone else. Refresh to see the latest.”
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-E1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2878,8 +2885,8 @@
         <is>
           <t>1. The save fails exactly as S2-E3: the alert “This work order can no longer be edited. Refresh to see the latest.” is shown and the entered data remains.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S3-E2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9318 (Story 3, Inline Edit Part - Tech View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S3-E2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2927,8 +2934,8 @@
         <is>
           <t>1. The inline row displays six editable fields, in order: description, part number, quantity, category, cost, sell price (Rate).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2976,8 +2983,8 @@
         <is>
           <t>1. Description, part number, and quantity behaviour from Story 2 applies identically (including the empty-required quantity and the optional part number).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3026,8 +3033,8 @@
           <t>1. Cost and sell price populate automatically from the selected part.
 2. Cost and sell price display with a $ prefix.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3076,8 +3083,8 @@
         <is>
           <t>1. The populated cost and sell price can both be overwritten by the user.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3127,8 +3134,8 @@
           <t>1. The category field is a select of the shop's part categories.
 2. A part saved with no category is assigned “Uncategorized”, consistent with the Tech View rule.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3176,8 +3183,8 @@
         <is>
           <t>1. The inline row displays a Save action, a “More Options” action, and an X (close) action.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R6, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R6, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3226,8 +3233,8 @@
           <t>1. The part saves; part number and category are optional.
 2. Omitting any of description, quantity, cost, or sell price blocks the save (see validation cases).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R7, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R7, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3277,8 +3284,8 @@
 2. The “Part added” success toast displays.
 3. A new empty inline row opens with the cursor in the description field.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R8, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R8, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3326,8 +3333,8 @@
         <is>
           <t>1. The part details modal opens.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R9, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R9, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3376,8 +3383,8 @@
         <is>
           <t>1. All values already entered in the inline row carry over into the corresponding fields of the modal.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R10, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R10, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3427,8 +3434,8 @@
           <t>1. The part is added, the modal closes, and the inline row also closes.
 2. No new inline row is opened.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R11, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R11, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3479,8 +3486,8 @@
           <t>1. The S6-R1 confirmation is shown first.
 2. On Discard the modal closes, the inline row closes, and the entered data is discarded.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R12, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R12, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3528,8 +3535,8 @@
         <is>
           <t>1. Pressing Enter saves the row, matching the Tech View behaviour.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R13, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R13, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3577,8 +3584,8 @@
         <is>
           <t>1. The “More Options” part details modal opens, so a user can escalate to full detail without the mouse.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R14, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R14, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3592,7 +3599,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Tab moves through all six fields in order then to Save</t>
+          <t>Tab moves through the Full View add row and never leaves it</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3619,16 +3626,18 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Place the cursor in the description field and press Tab repeatedly.</t>
+          <t>Place the cursor in the description field and press Tab repeatedly through the whole row.
+For the last step, have a bin allocated so the “Pulled from” chip is shown.</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. Tab moves the cursor forward in the order description, part number, quantity, category, cost, sell price.
-2. Tab from the sell price field moves focus to the Save action rather than leaving the row.
----
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R15, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+          <t>1. Tab moves the cursor forward through the row and does not leave it (per the spec's Keyboard Model — Inline Row).
+2. The Full View add-row Tab order is: description, part number, quantity, category, cost, sell price, Save, Cancel (X), then More Options (which sits visually to the left of Save but tabs last of the row's own controls).
+3. When a bin is allocated, the “Pulled from” bin chip (in the hint row below) is the final Tab stop; it is present only while a bin is allocated.
+---
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R15 and Keyboard Model - Inline Row, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3676,8 +3685,8 @@
         <is>
           <t>1. Escape closes the inline row, matching the Tech View behaviour.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R16, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R16, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3726,8 +3735,8 @@
         <is>
           <t>1. The inline row remains open and its data is preserved, matching the Tech View behaviour.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R17, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R17, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3777,8 +3786,8 @@
           <t>1. The keyboard hint legend additionally shows: ⇧Enter — more options.
 2. This hint is only shown to Full View users.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R18, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R18, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3826,8 +3835,8 @@
         <is>
           <t>1. The Requested flow applies equally in Full View: the part is added as Requested and flagged as needing details, with the “Part added” toast.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R19, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R19, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3878,8 +3887,8 @@
           <t>1. The typeahead ends with a “Create &lt;typed text&gt; as a new part” action that opens the part details modal with the typed description carried over.
 2. This action is shown to Full View users only and is not displayed in Tech View.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-R20, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-R20, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3928,8 +3937,8 @@
           <t>1. The row does not save and the single combined message names the missing fields in order, including cost and sell price (for example “Enter a cost and sell price to save this part.”).
 2. All validation behaviour from S2-N1 through S2-N6 applies.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-N1, S4-N2, S4-N3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-N1, S4-N2, S4-N3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3977,8 +3986,8 @@
         <is>
           <t>1. Validation is not enforced when More Options is selected; the user may escalate to the modal with an incomplete row, and the modal applies its own validation on save.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-N4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-N4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4027,8 +4036,8 @@
         <is>
           <t>1. The row does not save and the message names the field: “Cost must be a number.”, “Cost cannot be negative.”, “Sell price must be a number.”, “Sell price cannot be negative.” as applicable.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-N5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-N5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4077,8 +4086,8 @@
           <t>1. A non-blocking note is displayed in the row: “Sell price is below cost.”
 2. The row still saves — a sell price lower than the cost is permitted and does not block saving.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-N6, S4-E2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-N6, S4-E2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4127,8 +4136,8 @@
           <t>1. Those fields open empty and the user must enter them before saving inline.
 2. The user may instead select “More Options” to complete the part in the modal.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-E1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4177,8 +4186,8 @@
         <is>
           <t>1. The save fails exactly as S2-E3: the “This work order can no longer be edited. Refresh to see the latest.” alert is shown and the entered data remains.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-E3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-E3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4227,8 +4236,8 @@
         <is>
           <t>1. An alert toast is shown: “Couldn't add the part. Please try again.” and the inline row remains open with the entered data intact (S2-EH1).
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S4-EH1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9319 (Story 4, Inline Add Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S4-EH1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4277,8 +4286,8 @@
         <is>
           <t>1. The part details modal opens, pre-populated with the part's current values.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S5-R1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S5-R1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4327,8 +4336,8 @@
         <is>
           <t>1. There is no inline edit row for Full View users; the part line is not replaced by an editable row.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S5-R2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S5-R2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4379,8 +4388,8 @@
           <t>1. The part line is updated and the modal closes.
 2. No inline row opens afterward.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S5-R3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S5-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4429,8 +4438,8 @@
         <is>
           <t>1. The Edit control is not displayed.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S5-N1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S5-N1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4480,8 +4489,8 @@
         <is>
           <t>1. The changes are discarded and the part line is left unchanged.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S5-N2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S5-N2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4531,8 +4540,8 @@
         <is>
           <t>1. The S6-R5 confirmation applies before the part details modal opens.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S5-E1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9320 (Story 5, Edit Part - Full View) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S5-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4581,8 +4590,8 @@
           <t>1. A confirmation is displayed — Title: “Discard this part?”, Body: “The details you entered will be lost.”, Actions: “Keep Editing” and “Discard Part”.
 2. “Keep Editing” is the default focused action.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4631,8 +4640,8 @@
           <t>1. The same confirmation is shown with edit wording — Title: “Discard these changes?”, Body: “The changes you made will be lost.”
 2. Actions and default focus are unchanged: “Keep Editing” (default) and “Discard Part”.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4680,8 +4689,8 @@
         <is>
           <t>1. The confirmation closes and the user is returned to the inline row with all entered data intact.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4731,8 +4740,8 @@
           <t>1. On an add row the inline row closes without saving.
 2. On an edit row the part line returns to its previously saved values.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4781,8 +4790,8 @@
           <t>1. A confirmation is displayed — Title: “Leave without saving?”, Body: “This part hasn't been added to the work order yet. Leaving will discard it.”, Actions: “Stay on Work Order” and “Leave”.
 2. “Stay on Work Order” is the default focused action.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4833,8 +4842,8 @@
 2. Selecting “Discard Part” closes the current row and opens the requested one.
 3. Selecting “Keep Editing” cancels the request and leaves the current row open and focused.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4882,8 +4891,8 @@
         <is>
           <t>1. Only one inline row may be open on a work order at any time; opening another goes through the S6-R5 handling rather than opening a second row.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-R6, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-R6, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4931,8 +4940,8 @@
         <is>
           <t>1. The row closes immediately with no confirmation.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-N1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-N1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -4980,8 +4989,8 @@
         <is>
           <t>1. Navigation proceeds immediately with no confirmation.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-N2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-N2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5029,8 +5038,8 @@
         <is>
           <t>1. Closing it or navigating away proceeds immediately with no confirmation.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-N3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-N3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5078,8 +5087,8 @@
         <is>
           <t>1. Navigation is unaffected; no confirmation is shown.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-N4, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-N4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5127,8 +5136,8 @@
         <is>
           <t>1. Clicking outside is not treated as navigating away and never triggers a confirmation; the row stays open with its data intact.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-N5, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-N5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5176,8 +5185,8 @@
         <is>
           <t>1. The untouched follow-on empty row does not trigger any confirmation; navigation and dismissal proceed freely.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-E1, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5225,8 +5234,8 @@
         <is>
           <t>1. The entered part is discarded and the navigation the user requested is completed.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-E2, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-E2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5274,8 +5283,8 @@
         <is>
           <t>1. The navigation is cancelled, the user stays on the work order, and focus returns to the inline row with data intact.
 ---
-This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 13, section S6-E3, read on 25 August 2026.
-AUTOMATION: Not available on Build to test Yet - Last checked 8/25/2026</t>
+This is the expected behaviour as per epic SV-9315 and story SV-9321 (Story 6, Protecting Unsaved Part Data) and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S6-E3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5285,6 +5294,1153 @@
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Catalog part carries named bins with on-hand quantity and one Default</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+You can inspect a catalog part's bins (via the typeahead card, the bin picker, or the Bin Locations modal).</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Look at the set of bins on a catalog part that is held in stock.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1. Each catalog part carries a set of bins.
+2. Every bin has a name and an on-hand quantity.
+3. Exactly one bin per part is flagged as the Default bin.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R1)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Typeahead result cards show inventory quantity and bin chips</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Open the inline row and search the part number typeahead.
+Inspect a result card for a stocked part held across several bins.
+Inspect a result card for a part with no bins.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1. The result card shows the total inventory quantity across all bins, then up to three bin chips each with its per-bin quantity.
+2. When a part is in more than three bins, the further bins collapse into a “+ N” chip whose tooltip lists them.
+3. A part with no bins shows “Not stocked” in warning styling instead of chips.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R2)</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a part auto-allocates the full quantity to a single bin</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Select a catalog part whose Default bin covers the quantity and note the allocation.
+Select a part whose Default bin is below the quantity but another single bin covers it.
+Select a part where no single bin covers the quantity.</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. When the Default bin covers the quantity, the full quantity is allocated to the Default bin.
+2. When the Default bin is below the quantity, the full quantity is allocated to the largest single bin whose on-hand covers it.
+3. When no single bin covers the quantity, the allocation stays on the Default bin.
+4. The allocation is never split automatically.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R3, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R3)</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Allocation is shown below the row as a Pulled from chip</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Select a stocked catalog part and look below the inline row.
+Then clear the allocation / part so no allocation exists and look again.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. While an allocation exists, it is displayed below the row as “Pulled from” followed by a chip.
+2. The chip is displayed only while an allocation exists.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R4, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R4)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Chip label is the bin name for one bin and N bins for a split</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Allocate the whole quantity to a single bin and read the chip label.
+Split the quantity across two or more bins and read the chip label.</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>1. For a single-bin allocation the chip label is the bin name.
+2. For a split allocation the chip label reads “N bins” (where N is the number of bins).
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R5, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R5)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Selecting the chip opens a bin picker listing every bin</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+An allocation exists so the Pulled from chip is shown.</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Select the “Pulled from” chip.</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1. A picker opens listing every bin in catalog order, each with its on-hand quantity.
+2. A check marks the currently selected bin and a Default badge marks the Default bin.
+3. Any bin whose on-hand is below the requested quantity is shown in warning styling.
+4. The picker ends with a “Split across bins…” action.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R6, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R6)</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Choosing a bin from the picker moves the full quantity into it</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The bin picker is open.</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Choose a bin other than the current one from the picker.</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>1. The full quantity moves into the chosen bin.
+2. The allocation is now marked as manually chosen.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R7, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R7)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Allocating more than a bin holds is permitted and only warns</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Allocate a quantity larger than the chosen bin's on-hand quantity.
+Attempt to save.</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>1. Allocating more than a bin's on-hand quantity is permitted; the bin is allowed to go negative.
+2. The system warns but does not block the save.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R8, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R8)</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>A short single-bin allocation shows the takes-negative warning</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The full quantity is allocated to a single bin whose on-hand is below that quantity.</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Look at the chip and the note beside it.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1. The chip is shown in warning styling.
+2. This warning is displayed beside it: “Only &lt;on hand&gt; here. Pulling &lt;qty&gt; takes this bin negative.”
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R9, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R9)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Auto-switching off the Default bin shows an informational note</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The Default bin is below the quantity but another single bin covers it, so auto-allocation moved off the Default.</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>Look at the note beside the chip.</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>1. This informational note is displayed beside the chip: “Default bin &lt;name&gt; has &lt;on hand&gt;. Switched to a bin that covers &lt;qty&gt;.”
+2. It is shown only when the takes-negative warning (S7-R9) does not apply.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R10, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R10)</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Editing the quantity re-runs allocation per manual or automatic state</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>With a manually chosen single bin, change the quantity.
+With an automatic allocation, change the quantity.</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>1. When the user manually chose a single bin, that bin is kept and the new quantity is moved into it — it is not re-picked, and the takes-negative warning (S7-R9) applies if the bin no longer covers it.
+2. When the allocation was automatic, the auto-allocation rule (S7-R3) runs again for the new quantity.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R11, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R11)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Split across bins opens the right modal for each view mode</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The bin picker is open on an add row.</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>As a Tech View user, select “Split across bins…”.
+As a Full View user on the add row, select “Split across bins…”.</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>1. For a Tech View user, “Split across bins…” opens the Bin Locations modal.
+2. For a Full View user on the add row, it opens the part details modal instead, where a per-bin allocation table replaces the single quantity field and focus lands on the first bin input.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R12, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R12)</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Bin Locations modal lists a row per bin with Auto and Apply</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The Bin Locations modal is open via “Split across bins…”.</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Inspect the modal's rows and actions.
+Select the Auto action.</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>1. The modal lists one row per bin, each showing name, a Default badge, on-hand quantity, and an allocation input.
+2. An Auto action redistributes the quantity Default-first then largest-first.
+3. An Apply action is present.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R13, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R13)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Applying a split writes it back and sets quantity to the sum</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The Bin Locations modal is open with per-bin allocations entered.</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Enter allocations across two or more bins and select Apply.</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>1. The split is written back to the inline row.
+2. The row's quantity is set to the sum of the per-bin allocations.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R14, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R14)</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Already-negative bins show in error styling but do not block</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+At least one bin is already at a negative on-hand quantity.
+The Bin Locations modal is open.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Look at the row for the already-negative bin.
+Enter an allocation and Apply.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. Bins already at a negative on-hand quantity are displayed in error styling in the Bin Locations modal.
+2. Allocation is not blocked.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R15, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R15)</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Tech View edit row carries the same allocation UI and restores stored splits</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The work order line already has at least one part on it.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Open the Tech View inline edit row on a part that already has a stored allocation.
+Open the edit row on a part that has no stored allocation.</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>1. The inline edit row carries the same chip, picker, warnings and label format as the add row.
+2. When the part already has a stored allocation, it is restored and treated as manually chosen.
+3. When there is no stored allocation, auto-allocation runs.
+4. Full View has no inline edit row (S5-R2), so only Tech View reaches this path.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R16, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R16)</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Allocation is stored on save and not shown on the saved part row</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Allocate a bin, save the part, and look at the saved part row.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1. The allocation is stored with the part line on save.
+2. It is not displayed on the saved part row (surfacing it in the part detail panel is out of scope per the spec's §2).
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R17, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R17)</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>The Pulled from chip is reachable by Tab</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+An allocation exists so the Pulled from chip is shown.</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>From the row's last field, Tab toward the chip (per the spec's Keyboard Model — Inline Row).</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1. The “Pulled from” chip is reachable by Tab; it is the last Tab stop in the row's keyboard order, after Save and Cancel (X) (and after More Options in Full View).
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-R18 and Keyboard Model - Inline Row, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-R18)</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>A part with no bins gets no allocation and no chip</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Select a catalog part that is held in no bins (not stocked).</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>1. The part gets no allocation and no chip.
+2. The “Pulled from” line is not displayed.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-N1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-N1)</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>A part not linked to the catalog gets no allocation and no chip</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Free-type a description with no catalog part selected.</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>1. A part not linked to the catalog gets no allocation and no chip.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-N2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-N2)</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>No note is shown when the Default bin covers the quantity</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The Default bin's on-hand covers the quantity, and other bins would also cover it.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Select the part and look for a switched-bin note.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1. When the Default bin covers the quantity, no note is shown even if other bins would also cover it.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-E1, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-E1)</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>A split allocation never shows the takes-negative warning</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Inline Add and Edit Parts - Bin Allocation</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>A work order is open with status Estimate, Approved, In Progress, or Review.
+You have the 'Work Order Line - Create and Edit' setting enabled.
+Your 'Work Orders → Work Order View Mode' permission is set to Tech View.
+The row is linked to a catalog part that is held in at least one bin (a part with no bins is treated as not stocked and this story does not apply).
+The quantity is split across two or more bins.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Create a split allocation and look for the takes-negative warning.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1. A split allocation never shows the takes-negative warning from S7-R9; that warning applies only to a single-bin allocation.
+---
+This is the expected behaviour as per epic SV-9315 and Story 7 (Bin Allocation on the Inline Row); the Story 7 Jira ticket is TBD and the Inline Add and Edit Parts on Work Order Lines specification version 16, section S7-E2, read on 31 August 2026.
+AUTOMATION: Not available on Build to test Yet - Last checked 8/31/2026</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>SV-9315 (S7-E2)</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
